--- a/AAII_Financials/Quarterly/XVIPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XVIPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="92">
   <si>
     <t>XVIPY</t>
   </si>
@@ -656,77 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -766,8 +777,17 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +827,17 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +877,17 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +903,11 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +947,17 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +997,17 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1047,17 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1097,17 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1120,11 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,8 +1164,17 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1125,8 +1214,17 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1240,11 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1183,8 +1284,17 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,8 +1334,17 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1384,17 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1306,8 +1434,17 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1484,17 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1534,17 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1429,8 +1584,17 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1634,17 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1684,17 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1734,17 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1784,17 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1834,17 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1675,8 +1884,17 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1716,8 +1934,17 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1984,17 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,54 +2034,72 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2115,11 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,49 +2135,61 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F41" s="3">
+        <v>31700</v>
+      </c>
+      <c r="G41" s="3">
         <v>29700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>34000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>31500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>37500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>44400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>45400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>47800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>54300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>54500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>15900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>19100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1960,90 +2229,117 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F43" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G43" s="3">
         <v>16300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>19000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>18400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>12700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>18500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>16600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>15800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>11800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>12300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>12600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>12800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>23900</v>
+      </c>
+      <c r="F44" s="3">
+        <v>27000</v>
+      </c>
+      <c r="G44" s="3">
         <v>30200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>28300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>22500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>20500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>18700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>16400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>14100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>14100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>13400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>11500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>10700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2083,49 +2379,67 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>76100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>74700</v>
+      </c>
+      <c r="G46" s="3">
         <v>76200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>81300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>72400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>73500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>81600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>78300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>77700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>82200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>80200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>40000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>42600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2136,119 +2450,146 @@
         <v>4</v>
       </c>
       <c r="F47" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G47" s="3">
         <v>100</v>
       </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="H47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="J47" s="3">
         <v>100</v>
       </c>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>100</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>22600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>23200</v>
+      </c>
+      <c r="G48" s="3">
         <v>22000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>18700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>15100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>13500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>12000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>11400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>10300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>9700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>7200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>7200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>6200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>69600</v>
+      </c>
+      <c r="F49" s="3">
+        <v>70500</v>
+      </c>
+      <c r="G49" s="3">
         <v>70400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>70400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>67800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>66100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>61500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>60500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>60600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>61800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>60000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>61300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>61400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>60800</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2629,17 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2679,67 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>3100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>4200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>4100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>4200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>3600</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2779,67 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>260700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>259400</v>
+      </c>
+      <c r="F54" s="3">
+        <v>257600</v>
+      </c>
+      <c r="G54" s="3">
         <v>252300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>251100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>228600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>217100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>224600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>214500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>210800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>218300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>205300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>165800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>168000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>166300</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2855,11 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,8 +2875,11 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2497,55 +2889,64 @@
       <c r="E57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="F57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1000</v>
       </c>
       <c r="I58" s="3">
         <v>900</v>
@@ -2560,180 +2961,225 @@
         <v>900</v>
       </c>
       <c r="M58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
+        <v>900</v>
+      </c>
+      <c r="R58" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G59" s="3">
         <v>13000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>16100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>13000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>13900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>18000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>17700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>12200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>9700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>12000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14100</v>
+        <v>19500</v>
       </c>
       <c r="E60" s="3">
         <v>16900</v>
       </c>
       <c r="F60" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>14100</v>
+      </c>
+      <c r="H60" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I60" s="3">
         <v>13900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>16000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>14900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>19000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>18700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>13400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>13000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>10600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>12900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F61" s="3">
+        <v>12300</v>
+      </c>
+      <c r="G61" s="3">
         <v>12200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>10800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>2000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>2100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>1500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>1600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>1900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>2100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>1500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>1700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>200</v>
+      </c>
+      <c r="G62" s="3">
         <v>3800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>3300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>4300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>2900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>6500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>13800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>14200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>14500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3219,17 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3269,17 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3319,67 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>28300</v>
+      </c>
+      <c r="G66" s="3">
         <v>30100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>31100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>20200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>22200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>19200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>23400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>23400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>24900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>28400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>26400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>28300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3395,11 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3439,17 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3489,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3539,17 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3589,67 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>37100</v>
+      </c>
+      <c r="F72" s="3">
+        <v>34400</v>
+      </c>
+      <c r="G72" s="3">
         <v>30300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>29500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>27800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>26400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>25200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>16000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>13300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>11900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>4700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>4500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>4000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3689,17 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3739,17 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3789,67 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>228000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>229300</v>
+      </c>
+      <c r="G76" s="3">
         <v>222200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>220000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>208500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>194900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>205400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>191000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>187300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>193400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>176900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>139300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>139700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>137200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3889,72 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,8 +3994,17 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +4020,61 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
       </c>
       <c r="F83" s="3">
+        <v>800</v>
+      </c>
+      <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
+        <v>800</v>
+      </c>
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +4114,17 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +4164,17 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4214,17 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4264,17 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4314,67 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F89" s="3">
+        <v>9400</v>
+      </c>
+      <c r="G89" s="3">
         <v>2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>5600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>1800</v>
       </c>
       <c r="L89" s="3">
         <v>2300</v>
       </c>
       <c r="M89" s="3">
+        <v>100</v>
+      </c>
+      <c r="N89" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P89" s="3">
         <v>1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,49 +4390,61 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4484,17 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4534,67 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-6400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>-7600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>-5900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-10100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-4100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-4000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-5200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-4400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-3200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4610,11 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3953,8 +4654,17 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4704,17 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4754,17 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,25 +4804,34 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="E100" s="3">
-        <v>8600</v>
+        <v>-300</v>
       </c>
       <c r="F100" s="3">
         <v>-300</v>
       </c>
       <c r="G100" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="H100" s="3">
-        <v>-300</v>
+        <v>8600</v>
       </c>
       <c r="I100" s="3">
         <v>-300</v>
@@ -4103,100 +4840,127 @@
         <v>-200</v>
       </c>
       <c r="K100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>39200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-4600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>-9900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-3300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>38800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-4700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>-6500</v>
       </c>
     </row>
